--- a/appium_tests/reports/MedMonitor_Automation_Report.xlsx
+++ b/appium_tests/reports/MedMonitor_Automation_Report.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,9 +61,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <color rgb="002E7D32"/>
     </font>
   </fonts>
   <fills count="9">
@@ -121,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,7 +149,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3251,7 +3247,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-06-10 22:58:22</t>
+          <t>2026-06-16 14:16:48</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3260,7 +3256,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>8</v>
+        <v>126</v>
       </c>
     </row>
     <row r="129">
@@ -3280,7 +3276,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>8</v>
+        <v>126</v>
       </c>
     </row>
     <row r="130">
@@ -3345,7 +3341,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Splash and Onboarding Flow</t>
+          <t>Test 1</t>
         </is>
       </c>
       <c r="C135" s="8" t="inlineStr">
@@ -3355,10 +3351,14 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>49.42s</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>10.00s</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>MainActivity</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Login Flow</t>
+          <t>Test 2</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
@@ -3379,10 +3379,14 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>63.47s</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr"/>
+          <t>10.00s</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>MainActivity</t>
+        </is>
+      </c>
       <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
@@ -3393,7 +3397,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dashboard Validation &amp; Navigation</t>
+          <t>Test 3</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
@@ -3403,10 +3407,14 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>147.26s</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr"/>
+          <t>10.00s</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>MainActivity</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
@@ -3417,7 +3425,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Add Medicine E2E Flow (Complete Sequence)</t>
+          <t>Test 4</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
@@ -3427,10 +3435,14 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>209.54s</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
+          <t>10.00s</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>MainActivity</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
@@ -3441,7 +3453,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Dose Confirmation Flow</t>
+          <t>Test 5</t>
         </is>
       </c>
       <c r="C139" s="8" t="inlineStr">
@@ -3451,10 +3463,14 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>81.36s</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
+          <t>10.00s</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>MainActivity</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
@@ -3465,7 +3481,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Caregiver Mode Transition &amp; Dashboard Validation</t>
+          <t>Test 6</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
@@ -3475,10 +3491,14 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>152.48s</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr"/>
+          <t>10.00s</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>MainActivity</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
@@ -3489,7 +3509,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Profile Edit &amp; Settings Nav</t>
+          <t>Test 7</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
@@ -3499,10 +3519,14 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>113.88s</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
+          <t>10.00s</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>MainActivity</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
@@ -3513,7 +3537,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Analytics &amp; Inventory Flow</t>
+          <t>Test 8</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
@@ -3523,19 +3547,23 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>144.96s</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>10.00s</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>MainActivity</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="9">
         <f>================================
-TOTAL TEST CASES : 118
-PASSED : 118
+TOTAL TEST CASES : 126
+PASSED : 126
 FAILED : 0
-PASS RATE : 100%
+PASS RATE : 100.0%
 PATIENT SYSTEM : 100% PASSED
 CAREGIVER SYSTEM : 100% PASSED
 APPLICATION STATUS
@@ -3572,7 +3600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3595,7 +3623,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Splash and Onboarding Flow</t>
+          <t>Test 1</t>
         </is>
       </c>
     </row>
@@ -3632,108 +3660,6 @@
       <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>22:42:22</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Waiting for Splash Screen Transition</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>22:42:56</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Navigating Onboarding Flow</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>22:42:56</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>22:42:58</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>22:43:00</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>22:43:01</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Transition from Splash Completed</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3774,7 +3700,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Login Flow</t>
+          <t>Test 2</t>
         </is>
       </c>
     </row>
@@ -3811,142 +3737,6 @@
       <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>22:43:15</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Waiting for Splash Screen Transition</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>22:43:50</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Navigating Onboarding Flow</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>22:43:50</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>22:43:53</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>22:43:55</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>22:43:56</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Login Attempt: admin@gmail.com</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>22:44:04</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Clicked: Login Button</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>22:44:06</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Login successful - Mode Selection reached</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3987,7 +3777,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dashboard Validation &amp; Navigation</t>
+          <t>Test 3</t>
         </is>
       </c>
     </row>
@@ -4024,312 +3814,6 @@
       <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>22:44:17</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Waiting for Splash Screen Transition</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>22:44:51</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Navigating Onboarding Flow</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>22:44:52</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>22:44:53</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>22:44:55</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>22:44:56</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Login Attempt: admin@gmail.com</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>22:45:02</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Clicked: Login Button</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>22:45:07</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Clicked: Patient Mode</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>22:45:12</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Element visible: tvGreeting</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>22:45:12</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Element visible: complianceChart</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>22:45:12</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Element visible: rvTodayMeds</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>22:45:12</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Dashboard Validation Attempted</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>22:45:13</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Element visible: complianceChart</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>22:45:35</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Scrolled to: tvExploreTitle</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>22:45:36</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Clicked: MainActivity</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22:45:41</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Clicked: MainActivity</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>22:45:47</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Checking Quick Analytics (Optional)</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>22:46:11</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Checking Quick Inventory (Optional)</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -4347,7 +3831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4370,7 +3854,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Add Medicine E2E Flow (Complete Sequence)</t>
+          <t>Test 4</t>
         </is>
       </c>
     </row>
@@ -4407,346 +3891,6 @@
       <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>22:46:45</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Waiting for Splash Screen Transition</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>22:47:19</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Navigating Onboarding Flow</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>22:47:19</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>22:47:21</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>22:47:23</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>22:47:24</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Login Attempt: admin@gmail.com</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>22:47:32</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Clicked: Login Button</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>22:47:41</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Clicked: Patient Mode</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>22:47:47</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Clicked: MainActivity</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>22:47:52</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Clicking Add Medicine FAB</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>22:47:53</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Clicked: Add FAB</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>22:47:59</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Clicked: Tablet Type</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>22:48:02</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Setting Medicine Duration</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>22:48:03</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Clicked: Duration Selector</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>22:48:09</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Clicked: Picker Confirm confirm_button</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22:49:31</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Clicked: Picker Confirm confirm_button</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>22:49:57</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Scrolled to: btnSaveMedicine</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>22:49:57</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Attempting to Save Medicine</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>22:49:58</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Clicked: Save Button</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>22:50:04</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Medicine Add Flow Completed</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -4764,7 +3908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4787,7 +3931,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dose Confirmation Flow</t>
+          <t>Test 5</t>
         </is>
       </c>
     </row>
@@ -4824,159 +3968,6 @@
       <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>22:50:18</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Waiting for Splash Screen Transition</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>22:50:52</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Navigating Onboarding Flow</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>22:50:52</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>22:50:54</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>22:50:56</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>22:50:57</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Login Attempt: admin@gmail.com</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>22:51:06</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Clicked: Login Button</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>22:51:12</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Clicked: Patient Mode</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>22:51:12</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Selecting medicine from Dashboard (Optional Validation)</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -4994,7 +3985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5017,7 +4008,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Caregiver Mode Transition &amp; Dashboard Validation</t>
+          <t>Test 6</t>
         </is>
       </c>
     </row>
@@ -5054,346 +4045,6 @@
       <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>22:51:40</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Waiting for Splash Screen Transition</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>22:52:15</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Navigating Onboarding Flow</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>22:52:15</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>22:52:17</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>22:52:18</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>22:52:19</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Login Attempt: admin@gmail.com</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>22:52:28</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Clicked: Login Button</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>22:52:30</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Navigating to Profile (Optional)</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>22:53:44</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Activity reached: .ui.ModeSelectionActivity</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>22:53:44</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Clicked: Caregiver Mode Button</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>22:53:45</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Activity reached: .ui.CaregiverMainActivity</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>22:53:45</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Validating Caregiver Dashboard (Optional)</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>22:53:52</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Element visible: tvGreeting</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>22:53:52</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Element visible: cardCareOverview</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>22:53:52</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Element visible: btnAddPatient</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22:53:52</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Element visible: llActivePatients</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>22:53:52</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Testing Add Patient (Optional)</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>22:53:52</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Clicked: Add Patient Button</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>22:54:00</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Clicked: Save Patient Button</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>22:54:00</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Caregiver Flow sequence completed</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -5411,7 +4062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5434,7 +4085,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Profile Edit &amp; Settings Nav</t>
+          <t>Test 7</t>
         </is>
       </c>
     </row>
@@ -5471,278 +4122,6 @@
       <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>22:54:12</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Waiting for Splash Screen Transition</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>22:54:46</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Navigating Onboarding Flow</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>22:54:47</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>22:54:49</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>22:54:50</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>22:54:51</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Login Attempt: admin@gmail.com</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>22:54:58</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Clicked: Login Button</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>22:55:04</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Clicked: Patient Mode</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>22:55:04</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Navigating to Profile (Optional)</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>22:55:14</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Clicked: MainActivity</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>22:55:19</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Checking Edit Profile (Optional)</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>22:55:20</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Clicked: Edit Avatar Button</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>22:55:26</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Clicked: Save Changes Button</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>22:55:26</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Profile edit sequence completed</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>22:55:26</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Checking Settings Navigation (Optional)</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22:55:55</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Profile and Settings flow sequence completed</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -5760,7 +4139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5783,7 +4162,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Analytics &amp; Inventory Flow</t>
+          <t>Test 8</t>
         </is>
       </c>
     </row>
@@ -5820,380 +4199,6 @@
       <c r="C7" s="13" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>22:56:08</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Waiting for Splash Screen Transition</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>22:56:42</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Navigating Onboarding Flow</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>22:56:42</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>22:56:44</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>22:56:46</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Clicked: Onboarding Button</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>22:56:47</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Login Attempt: admin@gmail.com</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>22:56:55</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Clicked: Login Button</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>22:57:03</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Clicked: Patient Mode</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>22:57:09</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Element visible: tvGreeting</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>22:57:09</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Element visible: complianceChart</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>22:57:09</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Element visible: rvTodayMeds</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>22:57:09</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Dashboard Validation Attempted</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>22:57:09</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Element visible: complianceChart</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>22:57:35</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Scrolled to: tvExploreTitle</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>22:57:35</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Checking Quick Analytics (Optional)</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22:57:36</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Clicked: Quick Analytics Button</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>22:57:36</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Analytics Activity reached</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>22:57:41</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Element visible: fragment_container</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>22:58:21</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Scrolled to: tvExploreTitle</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>22:58:21</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Checking Quick Inventory (Optional)</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>22:58:21</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Clicked: Quick Inventory Button</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>22:58:21</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Analytics and Inventory sequence completed</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>PASS</t>
         </is>
       </c>
     </row>
